--- a/docs/intr_data.xlsx
+++ b/docs/intr_data.xlsx
@@ -1,31 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\intranet\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D5D253-99CF-441D-9955-A8B3B61235AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MENU" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="ROLE" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="MENU_ROLE" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="EMP_ROLE" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="EMP_INFO" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="ORG" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="RANK" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="TEMPLATE" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="PROJECT" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="COMMCODE" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="MENU" sheetId="1" r:id="rId1"/>
+    <sheet name="ROLE" sheetId="2" r:id="rId2"/>
+    <sheet name="MENU_ROLE" sheetId="3" r:id="rId3"/>
+    <sheet name="EMP_ROLE" sheetId="4" r:id="rId4"/>
+    <sheet name="EMP_INFO" sheetId="5" r:id="rId5"/>
+    <sheet name="ORG" sheetId="6" r:id="rId6"/>
+    <sheet name="RANK" sheetId="7" r:id="rId7"/>
+    <sheet name="TEMPLATE" sheetId="8" r:id="rId8"/>
+    <sheet name="PROJECT" sheetId="9" r:id="rId9"/>
+    <sheet name="COMMCODE" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="299">
   <si>
     <t>MENU</t>
   </si>
@@ -75,7 +79,7 @@
     <t>MENU_0003</t>
   </si>
   <si>
-    <t xml:space="preserve">회의 관리</t>
+    <t>회의 관리</t>
   </si>
   <si>
     <t>intrMtgInqy1010.do</t>
@@ -84,7 +88,7 @@
     <t>MENU_0004</t>
   </si>
   <si>
-    <t xml:space="preserve">일정 관리</t>
+    <t>일정 관리</t>
   </si>
   <si>
     <t>intrAprvInqy3010.do</t>
@@ -108,7 +112,7 @@
     <t>MENU_0007</t>
   </si>
   <si>
-    <t xml:space="preserve">기안 작성</t>
+    <t>기안 작성</t>
   </si>
   <si>
     <t>intrAprvInqy1010.do</t>
@@ -117,7 +121,7 @@
     <t>MENU_0008</t>
   </si>
   <si>
-    <t xml:space="preserve">결재 조회</t>
+    <t>결재 조회</t>
   </si>
   <si>
     <t>intrAprvInqy2010.do</t>
@@ -126,7 +130,7 @@
     <t>MENU_0009</t>
   </si>
   <si>
-    <t xml:space="preserve">결재선 관리</t>
+    <t>결재선 관리</t>
   </si>
   <si>
     <t>intrAprvInqy4010.do</t>
@@ -135,13 +139,13 @@
     <t>MENU_0010</t>
   </si>
   <si>
-    <t xml:space="preserve">업무 관리</t>
+    <t>업무 관리</t>
   </si>
   <si>
     <t>MENU_0011</t>
   </si>
   <si>
-    <t xml:space="preserve">업무일지 작성</t>
+    <t>업무일지 작성</t>
   </si>
   <si>
     <t>intrTaskInqy1010.do</t>
@@ -150,7 +154,7 @@
     <t>MENU_0012</t>
   </si>
   <si>
-    <t xml:space="preserve">업무 캘린더</t>
+    <t>업무 캘린더</t>
   </si>
   <si>
     <t>intrTaskInqy3010.do</t>
@@ -165,7 +169,7 @@
     <t>MENU_0014</t>
   </si>
   <si>
-    <t xml:space="preserve">사원 조회</t>
+    <t>사원 조회</t>
   </si>
   <si>
     <t>intrEmpInqy2010.do</t>
@@ -174,7 +178,7 @@
     <t>MENU_0015</t>
   </si>
   <si>
-    <t xml:space="preserve">담당업무 조회</t>
+    <t>담당업무 조회</t>
   </si>
   <si>
     <t>intrEmpInqy3010.do</t>
@@ -183,13 +187,13 @@
     <t>MENU_0016</t>
   </si>
   <si>
-    <t xml:space="preserve">공유정보 관리</t>
+    <t>공유정보 관리</t>
   </si>
   <si>
     <t>MENU_0017</t>
   </si>
   <si>
-    <t xml:space="preserve">공지사항 관리</t>
+    <t>공지사항 관리</t>
   </si>
   <si>
     <t>intrBoardInqy1010.do</t>
@@ -198,7 +202,7 @@
     <t>MENU_0018</t>
   </si>
   <si>
-    <t xml:space="preserve">배너 관리</t>
+    <t>배너 관리</t>
   </si>
   <si>
     <t>intrBanrInqy1010.do</t>
@@ -207,7 +211,7 @@
     <t>MENU_0019</t>
   </si>
   <si>
-    <t xml:space="preserve">업무일지 조회</t>
+    <t>업무일지 조회</t>
   </si>
   <si>
     <t>intrTaskInqy2010.do</t>
@@ -216,13 +220,13 @@
     <t>MENU_0020</t>
   </si>
   <si>
-    <t xml:space="preserve">전자결재 관리</t>
+    <t>전자결재 관리</t>
   </si>
   <si>
     <t>MENU_0021</t>
   </si>
   <si>
-    <t xml:space="preserve">결재양식 관리</t>
+    <t>결재양식 관리</t>
   </si>
   <si>
     <t>intrTempInqy1010.do</t>
@@ -231,7 +235,7 @@
     <t>MENU_0022</t>
   </si>
   <si>
-    <t xml:space="preserve">프로젝트 관리</t>
+    <t>프로젝트 관리</t>
   </si>
   <si>
     <t>intrProjInqy1010.do</t>
@@ -243,7 +247,7 @@
     <t>MENU_0024</t>
   </si>
   <si>
-    <t xml:space="preserve">사원 관리</t>
+    <t>사원 관리</t>
   </si>
   <si>
     <t>intrEmpInqy1010.do</t>
@@ -252,7 +256,7 @@
     <t>MENU_0025</t>
   </si>
   <si>
-    <t xml:space="preserve">인사 통계</t>
+    <t>인사 통계</t>
   </si>
   <si>
     <t>intrEmpInqy4010.do</t>
@@ -261,13 +265,13 @@
     <t>MENU_0026</t>
   </si>
   <si>
-    <t xml:space="preserve">시스템 관리</t>
+    <t>시스템 관리</t>
   </si>
   <si>
     <t>MENU_0027</t>
   </si>
   <si>
-    <t xml:space="preserve">권한 관리</t>
+    <t>권한 관리</t>
   </si>
   <si>
     <t>intrRoleInqy1010.do</t>
@@ -276,7 +280,7 @@
     <t>MENU_0028</t>
   </si>
   <si>
-    <t xml:space="preserve">메뉴 권한 부여</t>
+    <t>메뉴 권한 부여</t>
   </si>
   <si>
     <t>intrRoleInqy2010.do</t>
@@ -285,7 +289,7 @@
     <t>MENU_0029</t>
   </si>
   <si>
-    <t xml:space="preserve">사용자 권한 부여</t>
+    <t>사용자 권한 부여</t>
   </si>
   <si>
     <t>intrRoleInqy3010.do</t>
@@ -294,7 +298,7 @@
     <t>MENU_0030</t>
   </si>
   <si>
-    <t xml:space="preserve">로그 조회</t>
+    <t>로그 조회</t>
   </si>
   <si>
     <t>intrLogInqy1010.do</t>
@@ -303,7 +307,7 @@
     <t>MENU_0031</t>
   </si>
   <si>
-    <t xml:space="preserve">쿼리 입력</t>
+    <t>쿼리 입력</t>
   </si>
   <si>
     <t>intrQueryInqy1010.do</t>
@@ -324,13 +328,13 @@
     <t>ROLE_0001</t>
   </si>
   <si>
-    <t xml:space="preserve">관리자 권한</t>
+    <t>관리자 권한</t>
   </si>
   <si>
     <t>ROLE_0002</t>
   </si>
   <si>
-    <t xml:space="preserve">테스트 권한</t>
+    <t>테스트 권한</t>
   </si>
   <si>
     <t>MENU_ROLE</t>
@@ -600,13 +604,13 @@
     <t>TEMP_0001</t>
   </si>
   <si>
-    <t xml:space="preserve">휴가 신청서</t>
+    <t>휴가 신청서</t>
   </si>
   <si>
     <t>Leav</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+    <t>&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
  &lt;tbody&gt;
   &lt;tr&gt;
@@ -674,7 +678,7 @@
     <t>Exp</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+    <t>&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
  &lt;tbody&gt;
   &lt;tr&gt;
@@ -738,13 +742,13 @@
     <t>TEMP_0003</t>
   </si>
   <si>
-    <t xml:space="preserve">물품반출입 신청서</t>
+    <t>물품반출입 신청서</t>
   </si>
   <si>
     <t>Item</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;물품반출입 신청서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+    <t>&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;물품반출입 신청서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
  &lt;tbody&gt;
   &lt;tr&gt;
@@ -808,13 +812,13 @@
     <t>TEMP_0004</t>
   </si>
   <si>
-    <t xml:space="preserve">법인카드 정산서</t>
+    <t>법인카드 정산서</t>
   </si>
   <si>
     <t>Corp</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;법인카드 정산서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+    <t>&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;법인카드 정산서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border-color:currentcolor; border-image:none; border-style:none; border-width:medium; width:503px"&gt;
  &lt;tbody&gt;
   &lt;tr&gt;
@@ -908,7 +912,7 @@
     <t>PROJ_0001</t>
   </si>
   <si>
-    <t xml:space="preserve">내부 프로젝트</t>
+    <t>내부 프로젝트</t>
   </si>
   <si>
     <t>STAT_0020</t>
@@ -1097,7 +1101,7 @@
     <t>LOC_0010</t>
   </si>
   <si>
-    <t xml:space="preserve">회의실 (대)</t>
+    <t>회의실 (대)</t>
   </si>
   <si>
     <t>Loc</t>
@@ -1106,13 +1110,13 @@
     <t>LOC_0020</t>
   </si>
   <si>
-    <t xml:space="preserve">회의실 (중)</t>
+    <t>회의실 (중)</t>
   </si>
   <si>
     <t>LOC_0030</t>
   </si>
   <si>
-    <t xml:space="preserve">회의실 (소)</t>
+    <t>회의실 (소)</t>
   </si>
   <si>
     <t>PROC_0010</t>
@@ -1133,21 +1137,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;₩&quot;#,##0;[Red]\-&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="6" formatCode="&quot;₩&quot;#,##0;[Red]\-&quot;₩&quot;#,##0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="돋움"/>
+      <name val="G마켓 산스 Medium"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1160,16 +1173,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1184,43 +1198,43 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1240,291 +1254,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1715,3478 +1446,3468 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="2" style="1" width="15.625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="1" width="21.5"/>
-    <col customWidth="1" min="4" max="4" style="1" width="15.625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" style="1" width="21.625"/>
-    <col customWidth="1" min="6" max="8" style="1" width="15.625"/>
-    <col min="9" max="9" style="1" width="9"/>
-    <col customWidth="1" min="10" max="10" style="1" width="9"/>
-    <col min="11" max="16384" style="1" width="9"/>
+    <col min="1" max="2" width="15.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="21.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="15.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="9" style="5"/>
+    <col min="10" max="10" width="9" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>0</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4">
         <v>1</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="4"/>
       <c r="J3" s="6" t="str">
         <f t="shared" ref="J3:J32" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0001','0','공유정보','','','Y','1','');</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0001','0','공유정보','','','Y','1','');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>0</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4">
         <v>2</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="4"/>
       <c r="J4" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0002','0','공지사항','MENU_0001','intrBoardInqy2010.do','Y','2','');</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0002','0','공지사항','MENU_0001','intrBoardInqy2010.do','Y','2','');</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>0</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4">
         <v>3</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="4"/>
       <c r="J5" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0003','0','회의 관리','MENU_0001','intrMtgInqy1010.do','Y','3','');</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0003','0','회의 관리','MENU_0001','intrMtgInqy1010.do','Y','3','');</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>0</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="F6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4">
         <v>4</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="4"/>
       <c r="J6" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0004','0','일정 관리','MENU_0001','intrAprvInqy3010.do','Y','4','');</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0004','0','일정 관리','MENU_0001','intrAprvInqy3010.do','Y','4','');</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>0</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="4">
         <v>5</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="4"/>
       <c r="J7" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0005','0','내부규정','MENU_0001','intrRegsInqy1010.do','Y','5','');</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0005','0','내부규정','MENU_0001','intrRegsInqy1010.do','Y','5','');</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>0</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="4">
         <v>6</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="4"/>
       <c r="J8" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0006','0','전자결재','','','Y','6','');</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0006','0','전자결재','','','Y','6','');</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>0</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4">
         <v>7</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="4"/>
       <c r="J9" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0007','0','기안 작성','MENU_0006','intrAprvInqy1010.do','Y','7','');</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0007','0','기안 작성','MENU_0006','intrAprvInqy1010.do','Y','7','');</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>0</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="5">
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4">
         <v>8</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="4"/>
       <c r="J10" s="6" t="str">
         <f t="shared" ref="J10:J13" si="1">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A10&amp;"','"&amp;B10&amp;"','"&amp;C10&amp;"','"&amp;D10&amp;"','"&amp;E10&amp;"','"&amp;F10&amp;"','"&amp;G10&amp;"','"&amp;H10&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0008','0','결재 조회','MENU_0006','intrAprvInqy2010.do','Y','8','');</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0008','0','결재 조회','MENU_0006','intrAprvInqy2010.do','Y','8','');</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>0</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="5">
+      <c r="F11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="4">
         <v>9</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="4"/>
       <c r="J11" s="6" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0009','0','결재선 관리','MENU_0006','intrAprvInqy4010.do','Y','9','');</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0009','0','결재선 관리','MENU_0006','intrAprvInqy4010.do','Y','9','');</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>0</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="5">
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4">
         <v>10</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="4"/>
       <c r="J12" s="6" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0010','0','업무 관리','','','Y','10','');</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0010','0','업무 관리','','','Y','10','');</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>0</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="5">
-        <v>11</v>
-      </c>
-      <c r="H13" s="5"/>
+      <c r="F13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="4">
+        <v>11</v>
+      </c>
+      <c r="H13" s="4"/>
       <c r="J13" s="6" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0011','0','업무일지 작성','MENU_0010','intrTaskInqy1010.do','Y','11','');</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0011','0','업무일지 작성','MENU_0010','intrTaskInqy1010.do','Y','11','');</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>0</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="5">
+      <c r="F14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4">
         <v>12</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="4"/>
       <c r="J14" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0012','0','업무 캘린더','MENU_0010','intrTaskInqy3010.do','Y','12','');</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0012','0','업무 캘린더','MENU_0010','intrTaskInqy3010.do','Y','12','');</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>0</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="5">
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="4">
         <v>13</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="4"/>
       <c r="J15" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0013','0','인사정보','','','Y','13','');</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0013','0','인사정보','','','Y','13','');</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>0</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="5">
+      <c r="F16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="4">
         <v>14</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="4"/>
       <c r="J16" s="6" t="str">
         <f t="shared" ref="J16:J17" si="2">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A16&amp;"','"&amp;B16&amp;"','"&amp;C16&amp;"','"&amp;D16&amp;"','"&amp;E16&amp;"','"&amp;F16&amp;"','"&amp;G16&amp;"','"&amp;H16&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0014','0','사원 조회','MENU_0013','intrEmpInqy2010.do','Y','14','');</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0014','0','사원 조회','MENU_0013','intrEmpInqy2010.do','Y','14','');</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>0</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="5">
+      <c r="F17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="4">
         <v>15</v>
       </c>
-      <c r="H17" s="5"/>
+      <c r="H17" s="4"/>
       <c r="J17" s="6" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0015','0','담당업무 조회','MENU_0013','intrEmpInqy3010.do','Y','15','');</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0015','0','담당업무 조회','MENU_0013','intrEmpInqy3010.do','Y','15','');</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>1</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="5">
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="4">
         <v>16</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H18" s="4"/>
       <c r="J18" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0016','1','공유정보 관리','','','Y','16','');</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0016','1','공유정보 관리','','','Y','16','');</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>1</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="5">
+      <c r="F19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="4">
         <v>17</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="4"/>
       <c r="J19" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A19&amp;"','"&amp;B19&amp;"','"&amp;C19&amp;"','"&amp;D19&amp;"','"&amp;E19&amp;"','"&amp;F19&amp;"','"&amp;G19&amp;"','"&amp;H19&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0017','1','공지사항 관리','MENU_0016','intrBoardInqy1010.do','Y','17','');</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0017','1','공지사항 관리','MENU_0016','intrBoardInqy1010.do','Y','17','');</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="5">
+      <c r="F20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="4">
         <v>18</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="4"/>
       <c r="J20" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0018','1','배너 관리','MENU_0016','intrBanrInqy1010.do','Y','18','');</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0018','1','배너 관리','MENU_0016','intrBanrInqy1010.do','Y','18','');</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>1</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="5">
+      <c r="F21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="4">
         <v>19</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="4"/>
       <c r="J21" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A21&amp;"','"&amp;B21&amp;"','"&amp;C21&amp;"','"&amp;D21&amp;"','"&amp;E21&amp;"','"&amp;F21&amp;"','"&amp;G21&amp;"','"&amp;H21&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0019','1','업무일지 조회','MENU_0016','intrTaskInqy2010.do','Y','19','');</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0019','1','업무일지 조회','MENU_0016','intrTaskInqy2010.do','Y','19','');</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>1</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="5">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="4">
         <v>20</v>
       </c>
-      <c r="H22" s="5"/>
+      <c r="H22" s="4"/>
       <c r="J22" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0020','1','전자결재 관리','','','Y','20','');</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0020','1','전자결재 관리','','','Y','20','');</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>1</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="5">
+      <c r="F23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="4">
         <v>21</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="4"/>
       <c r="J23" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0021','1','결재양식 관리','MENU_0020','intrTempInqy1010.do','Y','21','');</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0021','1','결재양식 관리','MENU_0020','intrTempInqy1010.do','Y','21','');</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>1</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="5">
+      <c r="F24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="4">
         <v>22</v>
       </c>
-      <c r="H24" s="5"/>
+      <c r="H24" s="4"/>
       <c r="J24" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0022','1','프로젝트 관리','MENU_0020','intrProjInqy1010.do','Y','22','');</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0022','1','프로젝트 관리','MENU_0020','intrProjInqy1010.do','Y','22','');</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>1</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="5">
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="4">
         <v>23</v>
       </c>
-      <c r="H25" s="5"/>
+      <c r="H25" s="4"/>
       <c r="J25" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0023','1','인사정보','','','Y','23','');</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0023','1','인사정보','','','Y','23','');</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>1</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="5">
+      <c r="F26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="4">
         <v>24</v>
       </c>
-      <c r="H26" s="5"/>
+      <c r="H26" s="4"/>
       <c r="J26" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0024','1','사원 관리','MENU_0023','intrEmpInqy1010.do','Y','24','');</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0024','1','사원 관리','MENU_0023','intrEmpInqy1010.do','Y','24','');</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>1</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" s="5">
+      <c r="F27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="4">
         <v>25</v>
       </c>
-      <c r="H27" s="5"/>
+      <c r="H27" s="4"/>
       <c r="J27" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"','"&amp;F27&amp;"','"&amp;G27&amp;"','"&amp;H27&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0025','1','인사 통계','MENU_0023','intrEmpInqy4010.do','Y','25','');</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0025','1','인사 통계','MENU_0023','intrEmpInqy4010.do','Y','25','');</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>1</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="5">
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="4">
         <v>26</v>
       </c>
-      <c r="H28" s="5"/>
+      <c r="H28" s="4"/>
       <c r="J28" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0026','1','시스템 관리','','','Y','26','');</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0026','1','시스템 관리','','','Y','26','');</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>1</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="5">
+      <c r="F29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="4">
         <v>27</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="4"/>
       <c r="J29" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0027','1','권한 관리','MENU_0026','intrRoleInqy1010.do','Y','27','');</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0027','1','권한 관리','MENU_0026','intrRoleInqy1010.do','Y','27','');</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>1</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="5">
+      <c r="F30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="4">
         <v>28</v>
       </c>
-      <c r="H30" s="5"/>
+      <c r="H30" s="4"/>
       <c r="J30" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0028','1','메뉴 권한 부여','MENU_0026','intrRoleInqy2010.do','Y','28','');</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0028','1','메뉴 권한 부여','MENU_0026','intrRoleInqy2010.do','Y','28','');</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="4">
         <v>1</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31" s="5">
+      <c r="F31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="4">
         <v>29</v>
       </c>
-      <c r="H31" s="5"/>
+      <c r="H31" s="4"/>
       <c r="J31" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A31&amp;"','"&amp;B31&amp;"','"&amp;C31&amp;"','"&amp;D31&amp;"','"&amp;E31&amp;"','"&amp;F31&amp;"','"&amp;G31&amp;"','"&amp;H31&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0029','1','사용자 권한 부여','MENU_0026','intrRoleInqy3010.do','Y','29','');</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0029','1','사용자 권한 부여','MENU_0026','intrRoleInqy3010.do','Y','29','');</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>1</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32" s="5">
+      <c r="F32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="4">
         <v>30</v>
       </c>
-      <c r="H32" s="5"/>
+      <c r="H32" s="4"/>
       <c r="J32" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0030','1','로그 조회','MENU_0026','intrLogInqy1010.do','Y','30','');</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25">
-      <c r="A33" s="5" t="s">
+        <v>INSERT INTO MENU VALUES('MENU_0030','1','로그 조회','MENU_0026','intrLogInqy1010.do','Y','30','');</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>1</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="4">
         <v>31</v>
       </c>
-      <c r="H33" s="5"/>
-      <c r="I33" s="1"/>
+      <c r="H33" s="4"/>
       <c r="J33" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A33&amp;"','"&amp;B33&amp;"','"&amp;C33&amp;"','"&amp;D33&amp;"','"&amp;E33&amp;"','"&amp;F33&amp;"','"&amp;G33&amp;"','"&amp;H33&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0031','1','쿼리 입력','MENU_0026','intrQueryInqy1010.do','Y','31','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0031','1','쿼리 입력','MENU_0026','intrQueryInqy1010.do','Y','31','');</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="8" style="1" width="17.625"/>
-    <col min="9" max="16384" style="1" width="9"/>
+    <col min="1" max="2" width="17.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="19.25" style="5" customWidth="1"/>
+    <col min="4" max="8" width="17.625" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>20250520</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>80516</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4">
         <v>1</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="4"/>
       <c r="J3" s="6" t="str">
-        <f t="shared" ref="J3:J23" si="9">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('HIRE_0010','Y','Hire','20250520','80516','Y','1','');</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+        <f t="shared" ref="J3:J23" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"');"</f>
+        <v>INSERT INTO COMMCODE VALUES('HIRE_0010','Y','Hire','20250520','80516','Y','1','');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>20250520</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>80525</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4">
         <v>2</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="4"/>
       <c r="J4" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('HIRE_0020','N','Hire','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('HIRE_0020','N','Hire','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>20250520</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>80525</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4">
         <v>1</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="4"/>
       <c r="J5" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STAT_0010','진행','Stat','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('STAT_0010','진행','Stat','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>20250520</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>80525</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="F6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4">
         <v>2</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="4"/>
       <c r="J6" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STAT_0020','완료','Stat','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('STAT_0020','완료','Stat','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>20250520</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>80525</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="4">
         <v>3</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="4"/>
       <c r="J7" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STAT_0030','보류','Stat','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('STAT_0030','보류','Stat','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>20250520</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>80525</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="F8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="4">
         <v>1</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="4"/>
       <c r="J8" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0010','연차','Leav','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('LEAV_0010','연차','Leav','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>20250520</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>80525</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4">
         <v>2</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="4"/>
       <c r="J9" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0020','병가','Leav','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('LEAV_0020','병가','Leav','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>20250520</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>80525</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="5">
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4">
         <v>3</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="4"/>
       <c r="J10" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0030','경조휴가','Leav','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('LEAV_0030','경조휴가','Leav','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>20250520</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>80525</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="5">
+      <c r="F11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="4">
         <v>4</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="4"/>
       <c r="J11" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0040','반차','Leav','20250520','80525','Y','4','');</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('LEAV_0040','반차','Leav','20250520','80525','Y','4','');</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>20250520</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>80525</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="5">
+      <c r="F12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4">
         <v>5</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="4"/>
       <c r="J12" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0050','기타','Leav','20250520','80525','Y','5','');</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('LEAV_0050','기타','Leav','20250520','80525','Y','5','');</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>20250520</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>80525</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="5">
+      <c r="F13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="4">
         <v>1</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="4"/>
       <c r="J13" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PAY_0010','현금','Pay','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('PAY_0010','현금','Pay','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>20250520</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>80525</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="5">
+      <c r="F14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4">
         <v>2</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="4"/>
       <c r="J14" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PAY_0020','개인카드','Pay','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('PAY_0020','개인카드','Pay','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>20250520</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>80525</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="5">
+      <c r="F15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="4">
         <v>3</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="4"/>
       <c r="J15" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PAY_0030','전도금','Pay','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('PAY_0030','전도금','Pay','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>20250520</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>80525</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="5">
+      <c r="F16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="4">
         <v>1</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="4"/>
       <c r="J16" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('TYPE_0010','기안','Type','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('TYPE_0010','기안','Type','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>20250520</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>80525</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="5">
+      <c r="F17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="4">
         <v>2</v>
       </c>
-      <c r="H17" s="5"/>
+      <c r="H17" s="4"/>
       <c r="J17" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('TYPE_0020','결재','Type','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('TYPE_0020','결재','Type','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>20250520</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>80525</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="5">
+      <c r="F18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="4">
         <v>3</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H18" s="4"/>
       <c r="J18" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('TYPE_0030','참조','Type','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('TYPE_0030','참조','Type','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>20250520</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>80525</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="5">
+      <c r="F19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="4">
         <v>1</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="4"/>
       <c r="J19" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('REQ_0010','반입','Req','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('REQ_0010','반입','Req','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>20250520</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>80525</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="5">
+      <c r="F20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="4">
         <v>2</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="4"/>
       <c r="J20" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('REQ_0020','반출','Req','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('REQ_0020','반출','Req','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>20250520</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>80525</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="5">
+      <c r="F21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="4">
         <v>1</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="4"/>
       <c r="J21" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0010','결재진행중','Step','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('STEP_0010','결재진행중','Step','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>20250520</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <v>80525</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="5">
+      <c r="F22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="4">
         <v>2</v>
       </c>
-      <c r="H22" s="5"/>
+      <c r="H22" s="4"/>
       <c r="J22" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0020','결재완료','Step','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('STEP_0020','결재완료','Step','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <v>20250520</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>80525</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="5">
+      <c r="F23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="4">
         <v>3</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="4"/>
       <c r="J23" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0030','결재반송','Step','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO COMMCODE VALUES('STEP_0030','결재반송','Step','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>20250520</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <v>80525</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="5">
+      <c r="F24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="4">
         <v>4</v>
       </c>
-      <c r="H24" s="5"/>
+      <c r="H24" s="4"/>
       <c r="J24" s="6" t="str">
-        <f t="shared" ref="J24:J32" si="10">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A24&amp;"','"&amp;B24&amp;"','"&amp;C24&amp;"','"&amp;D24&amp;"','"&amp;E24&amp;"','"&amp;F24&amp;"','"&amp;G24&amp;"','"&amp;H24&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0040','결재취소','Step','20250520','80525','Y','4','');</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="s">
+        <f t="shared" ref="J24:J32" si="1">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A24&amp;"','"&amp;B24&amp;"','"&amp;C24&amp;"','"&amp;D24&amp;"','"&amp;E24&amp;"','"&amp;F24&amp;"','"&amp;G24&amp;"','"&amp;H24&amp;"');"</f>
+        <v>INSERT INTO COMMCODE VALUES('STEP_0040','결재취소','Step','20250520','80525','Y','4','');</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>20250520</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>80525</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="5">
+      <c r="F25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="4">
         <v>1</v>
       </c>
-      <c r="H25" s="5"/>
+      <c r="H25" s="4"/>
       <c r="J25" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('RSLT_0010','승인','Rslt','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO COMMCODE VALUES('RSLT_0010','승인','Rslt','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>20250520</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>80525</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="5">
+      <c r="F26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="4">
         <v>2</v>
       </c>
-      <c r="H26" s="5"/>
+      <c r="H26" s="4"/>
       <c r="J26" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('RSLT_0020','반송','Rslt','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO COMMCODE VALUES('RSLT_0020','반송','Rslt','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>20250520</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>80525</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" s="5">
+      <c r="F27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="4">
         <v>3</v>
       </c>
-      <c r="H27" s="5"/>
+      <c r="H27" s="4"/>
       <c r="J27" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('RSLT_0030','취소','Rslt','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO COMMCODE VALUES('RSLT_0030','취소','Rslt','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>20250520</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>80525</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="5">
+      <c r="F28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="4">
         <v>1</v>
       </c>
-      <c r="H28" s="5"/>
+      <c r="H28" s="4"/>
       <c r="J28" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LOC_0010','회의실 (대)','Loc','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO COMMCODE VALUES('LOC_0010','회의실 (대)','Loc','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="4">
         <v>20250520</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>80525</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="5">
+      <c r="F29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="4">
         <v>2</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="4"/>
       <c r="J29" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LOC_0020','회의실 (중)','Loc','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO COMMCODE VALUES('LOC_0020','회의실 (중)','Loc','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="4">
         <v>20250520</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="4">
         <v>80525</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="5">
+      <c r="F30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="4">
         <v>3</v>
       </c>
-      <c r="H30" s="5"/>
+      <c r="H30" s="4"/>
       <c r="J30" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LOC_0030','회의실 (소)','Loc','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5">
-      <c r="A31" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO COMMCODE VALUES('LOC_0030','회의실 (소)','Loc','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="4">
         <v>20250520</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="4">
         <v>80525</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="4">
         <v>1</v>
       </c>
-      <c r="H31" s="5"/>
-      <c r="I31" s="1"/>
+      <c r="H31" s="4"/>
       <c r="J31" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PROC_0010','조회','Proc','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5">
-      <c r="A32" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO COMMCODE VALUES('PROC_0010','조회','Proc','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="4">
         <v>20250520</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="4">
         <v>80525</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="4">
         <v>2</v>
       </c>
-      <c r="H32" s="5"/>
-      <c r="I32" s="1"/>
+      <c r="H32" s="4"/>
       <c r="J32" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PROC_0020','처리','Proc','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25">
-      <c r="A33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" ht="14.25">
-      <c r="A34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="J34" s="1"/>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO COMMCODE VALUES('PROC_0020','처리','Proc','20250520','80525','Y','2','');</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="5" style="1" width="15.625"/>
-    <col min="6" max="16384" style="1" width="9"/>
+    <col min="1" max="5" width="15.625" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="4"/>
       <c r="G3" s="6" t="str">
-        <f t="shared" ref="G3:G4" si="3">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO ROLE VALUES('ROLE_0001','관리자 권한','Y','1','');</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+        <f t="shared" ref="G3:G4" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"');"</f>
+        <v>INSERT INTO ROLE VALUES('ROLE_0001','관리자 권한','Y','1','');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>2</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="4"/>
       <c r="G4" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">INSERT INTO ROLE VALUES('ROLE_0002','테스트 권한','Y','2','');</v>
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ROLE VALUES('ROLE_0002','테스트 권한','Y','2','');</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="5" style="1" width="15.625"/>
-    <col min="6" max="16384" style="1" width="9"/>
+    <col min="1" max="5" width="15.625" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="4"/>
       <c r="G3" s="6" t="str">
-        <f t="shared" ref="G3:G26" si="4">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0001','Y','1','');</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+        <f t="shared" ref="G3:G26" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"');"</f>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0001','Y','1','');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>2</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="4"/>
       <c r="G4" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0002','Y','2','');</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0002','Y','2','');</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>3</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="4"/>
       <c r="G5" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0003','Y','3','');</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0003','Y','3','');</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>4</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="4"/>
       <c r="G6" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0004','Y','4','');</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0004','Y','4','');</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>5</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="4"/>
       <c r="G7" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0005','Y','5','');</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0005','Y','5','');</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>6</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="4"/>
       <c r="G8" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0006','Y','6','');</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0006','Y','6','');</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>7</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="4"/>
       <c r="G9" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0007','Y','7','');</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0007','Y','7','');</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>8</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="4"/>
       <c r="G10" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0008','Y','8','');</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0008','Y','8','');</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>9</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="4"/>
       <c r="G11" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0009','Y','9','');</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0009','Y','9','');</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>10</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="4"/>
       <c r="G12" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0010','Y','10','');</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0010','Y','10','');</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="5">
-        <v>11</v>
-      </c>
-      <c r="E13" s="5"/>
+      <c r="D13" s="4">
+        <v>11</v>
+      </c>
+      <c r="E13" s="4"/>
       <c r="G13" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0011','Y','11','');</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0011','Y','11','');</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>12</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="4"/>
       <c r="G14" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0012','Y','12','');</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0012','Y','12','');</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>13</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="4"/>
       <c r="G15" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0013','Y','13','');</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0013','Y','13','');</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>14</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="4"/>
       <c r="G16" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0014','Y','14','');</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0014','Y','14','');</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>15</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="4"/>
       <c r="G17" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0015','Y','15','');</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0015','Y','15','');</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>16</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="4"/>
       <c r="G18" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0016','Y','16','');</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0016','Y','16','');</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>17</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="4"/>
       <c r="G19" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0017','Y','17','');</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0017','Y','17','');</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>18</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="4"/>
       <c r="G20" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0018','Y','18','');</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0018','Y','18','');</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>19</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="4"/>
       <c r="G21" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0019','Y','19','');</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0019','Y','19','');</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>20</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="4"/>
       <c r="G22" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0020','Y','20','');</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0020','Y','20','');</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <v>21</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="4"/>
       <c r="G23" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0021','Y','21','');</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0021','Y','21','');</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>22</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="4"/>
       <c r="G24" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0022','Y','22','');</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0022','Y','22','');</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>23</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="4"/>
       <c r="G25" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0023','Y','23','');</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0023','Y','23','');</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>24</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="4"/>
       <c r="G26" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0024','Y','24','');</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0024','Y','24','');</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>25</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="4"/>
       <c r="G27" s="6" t="str">
-        <f t="shared" ref="G27:G33" si="5">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0025','Y','25','');</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="s">
+        <f t="shared" ref="G27:G33" si="1">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"');"</f>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0025','Y','25','');</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>26</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="4"/>
       <c r="G28" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0026','Y','26','');</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0026','Y','26','');</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="4">
         <v>27</v>
       </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="4"/>
       <c r="G29" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0027','Y','27','');</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0027','Y','27','');</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="4">
         <v>28</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="4"/>
       <c r="G30" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0028','Y','28','');</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0028','Y','28','');</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="4">
         <v>29</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="4"/>
       <c r="G31" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0029','Y','29','');</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0029','Y','29','');</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="4">
         <v>30</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="4"/>
       <c r="G32" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0030','Y','30','');</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5">
-      <c r="A33" s="5" t="s">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0030','Y','30','');</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="4">
         <v>31</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="1"/>
+      <c r="E33" s="4"/>
       <c r="G33" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0031','Y','31','');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0031','Y','31','');</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="5" style="1" width="15.625"/>
-    <col min="6" max="16384" style="1" width="9"/>
+    <col min="1" max="5" width="15.625" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="4"/>
       <c r="G3" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO EMP_ROLE VALUES('ROLE_0001','EMP_0001','Y','1','');</v>
+        <v>INSERT INTO EMP_ROLE VALUES('ROLE_0001','EMP_0001','Y','1','');</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="8" style="1" width="15.625"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" style="1" width="18.5"/>
-    <col customWidth="1" min="10" max="13" style="1" width="15.625"/>
-    <col min="14" max="16384" style="1" width="9"/>
+    <col min="1" max="8" width="15.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="15.625" style="5" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-    </row>
-    <row r="2" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="4">
         <v>20230814</v>
       </c>
-      <c r="M3" s="5"/>
+      <c r="M3" s="4"/>
       <c r="O3" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"','"&amp;J3&amp;"','"&amp;K3&amp;"','"&amp;L3&amp;"','"&amp;M3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO EMP_INFO VALUES('EMP_0001','ORG_0001','RANK_0001','ADMIN','Y','01077945147','','','jtax90@naver.com','ADMIN','+SsCQIbDOBIORGzUhrNPHA==','20230814','');</v>
+        <v>INSERT INTO EMP_INFO VALUES('EMP_0001','ORG_0001','RANK_0001','ADMIN','Y','01077945147','','','jtax90@naver.com','ADMIN','+SsCQIbDOBIORGzUhrNPHA==','20230814','');</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="8" style="1" width="15.625"/>
-    <col min="9" max="16384" style="1" width="9"/>
+    <col min="1" max="8" width="15.625" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
         <v>20230814</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4">
         <v>1</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="4"/>
       <c r="J3" s="6" t="str">
-        <f t="shared" ref="J3:J15" si="6">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0001','관리부','','20230814','000000','Y','1','');</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+        <f t="shared" ref="J3:J15" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"');"</f>
+        <v>INSERT INTO ORG VALUES('ORG_0001','관리부','','20230814','000000','Y','1','');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
         <v>20230814</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4">
         <v>2</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="4"/>
       <c r="J4" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0002','경영지원부','','20230814','000000','Y','2','');</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0002','경영지원부','','20230814','000000','Y','2','');</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
         <v>20230814</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4">
         <v>3</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="4"/>
       <c r="J5" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0003','인사부','','20230814','000000','Y','3','');</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0003','인사부','','20230814','000000','Y','3','');</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
         <v>20230814</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="F6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4">
         <v>4</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="4"/>
       <c r="J6" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0004','재무/회계부','','20230814','000000','Y','4','');</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0004','재무/회계부','','20230814','000000','Y','4','');</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4">
         <v>20230814</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="4">
         <v>5</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="4"/>
       <c r="J7" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0005','마케팅부','','20230814','000000','Y','5','');</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0005','마케팅부','','20230814','000000','Y','5','');</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4">
         <v>20230814</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="F8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="4">
         <v>6</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="4"/>
       <c r="J8" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0006','영업부','','20230814','000000','Y','6','');</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0006','영업부','','20230814','000000','Y','6','');</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4">
         <v>20230814</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4">
         <v>7</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="4"/>
       <c r="J9" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0007','기획부','','20230814','000000','Y','7','');</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0007','기획부','','20230814','000000','Y','7','');</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4">
         <v>20230814</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="5">
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4">
         <v>8</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="4"/>
       <c r="J10" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0008','생산부','','20230814','000000','Y','8','');</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0008','생산부','','20230814','000000','Y','8','');</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4">
         <v>20230814</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="5">
+      <c r="F11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="4">
         <v>9</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="4"/>
       <c r="J11" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0009','연구개발부','','20230814','000000','Y','9','');</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0009','연구개발부','','20230814','000000','Y','9','');</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4">
         <v>20230814</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="5">
+      <c r="F12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4">
         <v>10</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="4"/>
       <c r="J12" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0010','고객지원팀','','20230814','000000','Y','10','');</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0010','고객지원팀','','20230814','000000','Y','10','');</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5">
+      <c r="C13" s="4"/>
+      <c r="D13" s="4">
         <v>20230814</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="5">
-        <v>11</v>
-      </c>
-      <c r="H13" s="5"/>
+      <c r="F13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="4">
+        <v>11</v>
+      </c>
+      <c r="H13" s="4"/>
       <c r="J13" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0011','정보시스템팀','','20230814','000000','Y','11','');</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0011','정보시스템팀','','20230814','000000','Y','11','');</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4">
         <v>20230814</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="5">
+      <c r="F14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4">
         <v>12</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="4"/>
       <c r="J14" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0012','품질관리부','','20230814','000000','Y','12','');</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0012','품질관리부','','20230814','000000','Y','12','');</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4">
         <v>20230814</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="5">
+      <c r="F15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="4">
         <v>13</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="4"/>
       <c r="J15" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">INSERT INTO ORG VALUES('ORG_0013','법무팀','','20230814','000000','Y','13','');</v>
+        <f t="shared" si="0"/>
+        <v>INSERT INTO ORG VALUES('ORG_0013','법무팀','','20230814','000000','Y','13','');</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="7" style="1" width="15.625"/>
-    <col min="8" max="16384" style="1" width="9"/>
+    <col min="1" max="7" width="15.625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>20230814</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4">
         <v>1</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="4"/>
       <c r="I3" s="6" t="str">
-        <f t="shared" ref="I3:I12" si="7">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO RANK VALUES('RANK_0001','관리자','20230814','000000','Y','1','');</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+        <f t="shared" ref="I3:I12" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"');"</f>
+        <v>INSERT INTO RANK VALUES('RANK_0001','관리자','20230814','000000','Y','1','');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>20230814</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4">
         <v>2</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="4"/>
       <c r="I4" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">INSERT INTO RANK VALUES('RANK_0002','대표','20230814','000000','Y','2','');</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO RANK VALUES('RANK_0002','대표','20230814','000000','Y','2','');</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>20230814</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="E5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4">
         <v>3</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="4"/>
       <c r="I5" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">INSERT INTO RANK VALUES('RANK_0003','이사','20230814','000000','Y','3','');</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO RANK VALUES('RANK_0003','이사','20230814','000000','Y','3','');</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>20230814</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="4">
         <v>4</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="4"/>
       <c r="I6" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">INSERT INTO RANK VALUES('RANK_0004','팀장','20230814','000000','Y','4','');</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO RANK VALUES('RANK_0004','팀장','20230814','000000','Y','4','');</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>20230814</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="4">
         <v>5</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="4"/>
       <c r="I7" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">INSERT INTO RANK VALUES('RANK_0005','부장','20230814','000000','Y','5','');</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO RANK VALUES('RANK_0005','부장','20230814','000000','Y','5','');</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>20230814</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="4">
         <v>6</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="4"/>
       <c r="I8" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">INSERT INTO RANK VALUES('RANK_0006','차장','20230814','000000','Y','6','');</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO RANK VALUES('RANK_0006','차장','20230814','000000','Y','6','');</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>20230814</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="4">
         <v>7</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="4"/>
       <c r="I9" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">INSERT INTO RANK VALUES('RANK_0007','과장','20230814','000000','Y','7','');</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO RANK VALUES('RANK_0007','과장','20230814','000000','Y','7','');</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>20230814</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="E10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="4">
         <v>8</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="4"/>
       <c r="I10" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">INSERT INTO RANK VALUES('RANK_0008','대리','20230814','000000','Y','8','');</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO RANK VALUES('RANK_0008','대리','20230814','000000','Y','8','');</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>20230814</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="E11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4">
         <v>9</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="4"/>
       <c r="I11" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">INSERT INTO RANK VALUES('RANK_0009','주임','20230814','000000','Y','9','');</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO RANK VALUES('RANK_0009','주임','20230814','000000','Y','9','');</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>20230814</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="5">
+      <c r="E12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="4">
         <v>10</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="4"/>
       <c r="I12" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">INSERT INTO RANK VALUES('RANK_0010','사원','20230814','000000','Y','10','');</v>
+        <f t="shared" si="0"/>
+        <v>INSERT INTO RANK VALUES('RANK_0010','사원','20230814','000000','Y','10','');</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="3" style="1" width="17.625"/>
-    <col customWidth="1" min="4" max="4" style="1" width="61.75"/>
-    <col customWidth="1" min="5" max="5" style="1" width="17.8515625"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" style="1" width="17.875"/>
-    <col customWidth="1" min="7" max="9" style="1" width="17.625"/>
-    <col min="10" max="16384" style="1" width="9"/>
+    <col min="1" max="3" width="17.625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="61.75" style="5" customWidth="1"/>
+    <col min="5" max="5" width="17.875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="17.625" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>192</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -5195,20 +4916,19 @@
       <c r="E3" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="4">
         <v>1</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="1"/>
+      <c r="I3" s="4"/>
       <c r="K3" s="6" t="str">
-        <f t="shared" ref="K3:K6" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0001','휴가 신청서','Leav','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+        <f t="shared" ref="K3:K6" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"');"</f>
+        <v>INSERT INTO TEMPLATE VALUES('TEMP_0001','휴가 신청서','Leav','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
  &lt;tbody&gt;
   &lt;tr&gt;
@@ -5261,14 +4981,14 @@
 &lt;/table&gt;','intrAprvInqy1020.do','intrAprvInqy2020.do','Y','1','');</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>198</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -5277,20 +4997,19 @@
       <c r="E4" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="4">
         <v>2</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="1"/>
+      <c r="I4" s="4"/>
       <c r="K4" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0002','가지급결의서','Exp','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+        <f t="shared" si="0"/>
+        <v>INSERT INTO TEMPLATE VALUES('TEMP_0002','가지급결의서','Exp','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
  &lt;tbody&gt;
   &lt;tr&gt;
@@ -5345,14 +5064,14 @@
 &lt;/table&gt;','intrAprvInqy1021.do','intrAprvInqy2021.do','Y','2','');</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>204</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -5361,20 +5080,19 @@
       <c r="E5" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="G5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="4">
         <v>3</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="1"/>
+      <c r="I5" s="4"/>
       <c r="K5" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0003','물품반출입 신청서','Item','&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;물품반출입 신청서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+        <f t="shared" si="0"/>
+        <v>INSERT INTO TEMPLATE VALUES('TEMP_0003','물품반출입 신청서','Item','&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;물품반출입 신청서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
  &lt;tbody&gt;
   &lt;tr&gt;
@@ -5429,14 +5147,14 @@
 &lt;/table&gt;','intrAprvInqy1022.do','intrAprvInqy2022.do','Y','3','');</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>210</v>
       </c>
       <c r="D6" s="8" t="s">
@@ -5445,20 +5163,19 @@
       <c r="E6" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="G6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="4">
         <v>4</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="1"/>
+      <c r="I6" s="4"/>
       <c r="K6" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0004','법인카드 정산서','Corp','&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;법인카드 정산서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+        <f t="shared" si="0"/>
+        <v>INSERT INTO TEMPLATE VALUES('TEMP_0004','법인카드 정산서','Corp','&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;법인카드 정산서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border-color:currentcolor; border-image:none; border-style:none; border-width:medium; width:503px"&gt;
  &lt;tbody&gt;
   &lt;tr&gt;
@@ -5513,126 +5230,123 @@
 &lt;/table&gt;','intrAprvInqy1023.do','intrAprvInqy2023.do','Y','4','');</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1"/>
-    <row r="9" ht="17.25" customHeight="1"/>
-    <row r="10" ht="17.25" customHeight="1"/>
-    <row r="11" ht="14.25">
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" ht="16.5" customHeight="1"/>
-    <row r="14" ht="16.5" customHeight="1"/>
+    <row r="7" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="15" style="1" width="17.625"/>
-    <col min="16" max="16384" style="1" width="9"/>
+    <col min="1" max="15" width="17.625" style="5" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-    </row>
-    <row r="2" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>19900101</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>19901231</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>124</v>
       </c>
       <c r="H3" s="9">
         <v>0</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
         <v>124</v>
       </c>
       <c r="K3" s="7" t="s">
@@ -5641,28 +5355,24 @@
       <c r="L3" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="5">
+      <c r="M3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="4">
         <v>1</v>
       </c>
-      <c r="O3" s="5"/>
+      <c r="O3" s="4"/>
       <c r="Q3" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"','"&amp;J3&amp;"','"&amp;K3&amp;"','"&amp;L3&amp;"','"&amp;M3&amp;"','"&amp;N3&amp;"','"&amp;O3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO PROJECT VALUES('PROJ_0001','내부 프로젝트','내부 프로젝트','19900101','19901231','STAT_0020','EMP_0001','0','','EMP_0001','000000','000000','Y','1','');</v>
-      </c>
-    </row>
-    <row r="8" ht="13.5">
-      <c r="H8" s="1"/>
+        <v>INSERT INTO PROJECT VALUES('PROJ_0001','내부 프로젝트','내부 프로젝트','19900101','19901231','STAT_0020','EMP_0001','0','','EMP_0001','000000','000000','Y','1','');</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>